--- a/screener/results/shortlist_report_2026-07-18.xlsx
+++ b/screener/results/shortlist_report_2026-07-18.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Shortlist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Auction Overlay" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Harmonics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shortlist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auction Overlay" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harmonics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -66,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -112,9 +112,6 @@
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
@@ -2199,7 +2196,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>GSBD</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2208,10 +2205,10 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>65.5</v>
+        <v>72.5</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2220,7 +2217,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -2229,13 +2226,13 @@
         </is>
       </c>
       <c r="H5" s="12" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>0.74</v>
+        <v>0.44</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>511.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="6">
@@ -2250,14 +2247,14 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>59.5</v>
+        <v>69.5</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -2271,19 +2268,19 @@
         </is>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>763.5</v>
+        <v>722.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2292,10 +2289,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>57.5</v>
+        <v>59.5</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -2313,13 +2310,13 @@
         </is>
       </c>
       <c r="H7" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>1.34</v>
+        <v>0.74</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>28.1</v>
+        <v>531.2</v>
       </c>
     </row>
     <row r="8">
@@ -2334,10 +2331,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>57.5</v>
+        <v>51.5</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2355,19 +2352,19 @@
         </is>
       </c>
       <c r="H8" s="12" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>52.5</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>DAVA</t>
+          <t>AGNT</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -2376,14 +2373,14 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -2397,19 +2394,19 @@
         </is>
       </c>
       <c r="H9" s="12" t="n">
-        <v>2.27</v>
+        <v>1.06</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>SMPL</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2418,7 +2415,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>49</v>
+        <v>41.5</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>3</v>
@@ -2439,19 +2436,19 @@
         </is>
       </c>
       <c r="H10" s="12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>0.74</v>
+        <v>0.96</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>249.3</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>NMFC</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2460,10 +2457,10 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>46.5</v>
+        <v>39</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2481,19 +2478,19 @@
         </is>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0.91</v>
+        <v>0.03</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1.51</v>
+        <v>0.62</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>27.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2502,10 +2499,10 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>46.5</v>
+        <v>39</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2523,19 +2520,19 @@
         </is>
       </c>
       <c r="H12" s="12" t="n">
-        <v>0.59</v>
+        <v>0.12</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1130.7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>BCIC</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2544,10 +2541,10 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>41.5</v>
+        <v>34</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -2568,28 +2565,28 @@
         <v>0.14</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>0.4</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -2607,40 +2604,40 @@
         </is>
       </c>
       <c r="H14" s="12" t="n">
-        <v>0.28</v>
+        <v>0.47</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>72.59999999999999</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>LIGHT.AS</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>failed auction low</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>39</v>
+        <v>32.5</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>−</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -2649,19 +2646,19 @@
         </is>
       </c>
       <c r="H15" s="12" t="n">
-        <v>0.24</v>
+        <v>1.03</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>60.2</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>BCIC</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2670,10 +2667,10 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>39</v>
+        <v>31.5</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -2691,40 +2688,40 @@
         </is>
       </c>
       <c r="H16" s="12" t="n">
-        <v>0.49</v>
+        <v>0.13</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>167</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>GSBD</t>
+          <t>DAVA</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>rejection at highs</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>38</v>
+        <v>31.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -2733,31 +2730,31 @@
         </is>
       </c>
       <c r="H17" s="12" t="n">
-        <v>0.29</v>
+        <v>2.19</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>0.48</v>
+        <v>1.45</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>8.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>VRRM</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>37.5</v>
+        <v>31.5</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -2766,7 +2763,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -2775,35 +2772,35 @@
         </is>
       </c>
       <c r="H18" s="12" t="n">
-        <v>0.68</v>
+        <v>0.14</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.66</v>
+        <v>1.11</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>72.7</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>NMFC</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>36.5</v>
+        <v>31.5</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2817,35 +2814,35 @@
         </is>
       </c>
       <c r="H19" s="12" t="n">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0.64</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>4.1</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>SGA</t>
+          <t>PBH</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>36.5</v>
+        <v>31.5</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2859,19 +2856,19 @@
         </is>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>0.1</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>GPMT</t>
+          <t>FVRR</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2880,10 +2877,10 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2897,35 +2894,35 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" s="12" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>1.49</v>
+        <v>1.06</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>0.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>OTEX.TO</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>35</v>
+        <v>26.5</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2934,7 +2931,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -2943,35 +2940,35 @@
         </is>
       </c>
       <c r="H22" s="12" t="n">
-        <v>2</v>
+        <v>0.32</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>294.4</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>SMPL</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>34</v>
+        <v>26.5</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2985,31 +2982,31 @@
         </is>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>25.1</v>
+        <v>216.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>GIB</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>rejection at highs</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>34</v>
+        <v>26.5</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3027,35 +3024,35 @@
         </is>
       </c>
       <c r="H24" s="12" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>223</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>34</v>
+        <v>26.5</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -3069,35 +3066,35 @@
         </is>
       </c>
       <c r="H25" s="12" t="n">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>60.5</v>
+        <v>156.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>AGNT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>rejection at highs</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>34</v>
+        <v>26.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -3111,35 +3108,35 @@
         </is>
       </c>
       <c r="H26" s="12" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>1.52</v>
+        <v>0.75</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>6.6</v>
+        <v>280.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>32.5</v>
+        <v>25.5</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -3153,19 +3150,19 @@
         </is>
       </c>
       <c r="H27" s="12" t="n">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>1.03</v>
+        <v>0.65</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>0.6</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>ABR</t>
+          <t>SAMG</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -3174,10 +3171,10 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -3191,39 +3188,39 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="12" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>20.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>PBH</t>
+          <t>ABR</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>failed auction low</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -3237,31 +3234,31 @@
         </is>
       </c>
       <c r="H29" s="12" t="n">
-        <v>0.67</v>
+        <v>3.07</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0.99</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>29.5</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -3270,7 +3267,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -3279,35 +3276,35 @@
         </is>
       </c>
       <c r="H30" s="12" t="n">
-        <v>0.26</v>
+        <v>1.02</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>41.1</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>PET.TO</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3321,35 +3318,35 @@
         </is>
       </c>
       <c r="H31" s="12" t="n">
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0.77</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>441</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>FVRR</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -3363,31 +3360,31 @@
         </is>
       </c>
       <c r="H32" s="12" t="n">
-        <v>2.87</v>
+        <v>0.19</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>9.6</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>GIB</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>rejection at highs</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>26.5</v>
+        <v>24</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -3405,40 +3402,40 @@
         </is>
       </c>
       <c r="H33" s="12" t="n">
-        <v>0.08</v>
+        <v>1.62</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>0.68</v>
+        <v>1.5</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>37.9</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>OTEX.TO</t>
+          <t>MMS</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>failed auction low</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>26.5</v>
+        <v>20</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>−</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -3447,19 +3444,19 @@
         </is>
       </c>
       <c r="H34" s="12" t="n">
-        <v>0.21</v>
+        <v>1.35</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>41.3</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>GIB-A.TO</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3468,40 +3465,38 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>26.5</v>
+        <v>20</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>0.11</v>
-      </c>
+      <c r="H35" s="14" t="n"/>
       <c r="I35" s="12" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>62.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3510,10 +3505,10 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -3522,7 +3517,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -3531,40 +3526,40 @@
         </is>
       </c>
       <c r="H36" s="12" t="n">
-        <v>0.79</v>
+        <v>0.45</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>1.13</v>
+        <v>0.85</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>4.2</v>
+        <v>1145.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>LIGHT.AS</t>
+          <t>GIB-A.TO</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -3573,19 +3568,19 @@
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0.68</v>
+        <v>0.15</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>9.699999999999999</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -3594,10 +3589,10 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
@@ -3615,19 +3610,19 @@
         </is>
       </c>
       <c r="H38" s="12" t="n">
-        <v>1.37</v>
+        <v>0.27</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>52.1</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>VRRM</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3636,7 +3631,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>0</v>
@@ -3657,35 +3652,35 @@
         </is>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>28.4</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>PET.TO</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>rejection at highs</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -3699,19 +3694,19 @@
         </is>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0.79</v>
+        <v>1.39</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -3720,10 +3715,10 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
@@ -3732,28 +3727,26 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>−</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>0.25</v>
-      </c>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="n"/>
       <c r="I41" s="12" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>46</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>JBI</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -3762,40 +3755,40 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H42" s="12" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>1.3</v>
+        <v>0.84</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>42.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>BRSL</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -3804,19 +3797,19 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>−</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -3825,19 +3818,19 @@
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>0.49</v>
+        <v>1.94</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>22.2</v>
+        <v>308.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3846,10 +3839,10 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -3858,7 +3851,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>−</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -3867,19 +3860,19 @@
         </is>
       </c>
       <c r="H44" s="12" t="n">
-        <v>0.02</v>
+        <v>3.61</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>1.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v>1.9</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -3888,10 +3881,10 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
@@ -3900,7 +3893,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>−</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -3909,19 +3902,19 @@
         </is>
       </c>
       <c r="H45" s="12" t="n">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>0.84</v>
+        <v>1.07</v>
       </c>
       <c r="J45" s="13" t="n">
-        <v>168.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>SGA</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3930,7 +3923,7 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>0</v>
@@ -3947,21 +3940,23 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>1.04</v>
+      </c>
       <c r="I46" s="12" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>134.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>JBI</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -3970,7 +3965,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>0</v>
@@ -3991,13 +3986,13 @@
         </is>
       </c>
       <c r="H47" s="12" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>0.83</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>7.4</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48">
@@ -4012,10 +4007,10 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
@@ -4033,19 +4028,19 @@
         </is>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -4054,10 +4049,10 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -4071,21 +4066,23 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>0.78</v>
+      </c>
       <c r="I49" s="12" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="J49" s="13" t="n">
-        <v>3</v>
+        <v>451</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>GPMT</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -4094,10 +4091,10 @@
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
@@ -4114,14 +4111,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H50" s="12" t="n">
-        <v>2.71</v>
-      </c>
+      <c r="H50" s="14" t="n"/>
       <c r="I50" s="12" t="n">
-        <v>0.68</v>
+        <v>1.44</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>128.3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="51">
@@ -4139,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
@@ -4156,12 +4151,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H51" s="16" t="n"/>
-      <c r="I51" s="17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J51" s="18" t="n">
-        <v>0.2</v>
+      <c r="H51" s="16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I51" s="16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J51" s="17" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -4175,7 +4172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4241,7 +4238,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>GSBD</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4256,25 +4253,25 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Alternate Bat, Bat, Butterfly, Crab, Cypher, Deep Crab, Shark</t>
+          <t>ABCD</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>59.5</v>
+        <v>72.5</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>accepted breakout</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -4289,25 +4286,25 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Crab</t>
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>39</v>
+        <v>69.5</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>failed auction low</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>DLB</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -4322,30 +4319,30 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Alternate Bat, Bat, Butterfly, Crab, Cypher, Gartley, Shark</t>
+          <t>ABCD Ext</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>39</v>
+        <v>51.5</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>accepted breakout</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NMFC</t>
+          <t>DLB</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4355,25 +4352,25 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Butterfly, Crab</t>
+          <t>ABCD Ext</t>
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>36.5</v>
+        <v>51.5</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>accepted breakout</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SGA</t>
+          <t>NMFC</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -4388,14 +4385,14 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Butterfly, Crab, Deep Crab</t>
+          <t>ABCD</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>36.5</v>
+        <v>39</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
@@ -4406,12 +4403,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>NMFC</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -4421,14 +4418,14 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Alternate Bat, Bat, Butterfly, Crab, Deep Crab, Gartley, Shark</t>
+          <t>ABCD, AB=CD</t>
         </is>
       </c>
       <c r="E10" s="11" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -4439,12 +4436,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>SMPL</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -4454,14 +4451,14 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Crab, Cypher, Deep Crab, Gartley, Shark</t>
+          <t>ABCD Ext</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
@@ -4472,7 +4469,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>AGNT</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -4487,30 +4484,30 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Bat, Butterfly, Gartley</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="E12" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>34</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4520,14 +4517,14 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Bat, Butterfly, Crab, Gartley, Shark</t>
+          <t>Crab</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
@@ -4538,7 +4535,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>LIGHT.AS</t>
+          <t>BCIC</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -4553,30 +4550,30 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Alternate Bat, Bat, Butterfly, Crab, Deep Crab, Shark</t>
+          <t>Bat, ABCD, ABCD Ext</t>
         </is>
       </c>
       <c r="E14" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>25</v>
+        <v>31.5</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4586,14 +4583,14 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Butterfly, Deep Crab, Shark</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>24</v>
+        <v>31.5</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
@@ -4604,12 +4601,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>OTEX.TO</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4619,14 +4616,14 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Crab, Deep Crab, Gartley, Shark</t>
+          <t>Cypher</t>
         </is>
       </c>
       <c r="E16" s="11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>19</v>
+        <v>26.5</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
@@ -4637,12 +4634,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>CINT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -4652,14 +4649,14 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Deep Crab</t>
+          <t>ABCD</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>12.5</v>
+        <v>26.5</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
@@ -4670,7 +4667,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ABR</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -4685,47 +4682,47 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Crab, Deep Crab</t>
+          <t>Deep Crab</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>7.5</v>
+        <v>25</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>failed auction low</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>DAVA</t>
+          <t>MMS</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>sell</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Cypher</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>51.5</v>
+        <v>20</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
@@ -4736,17 +4733,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>sell</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -4755,43 +4752,43 @@
         </is>
       </c>
       <c r="E20" s="11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>failed auction low</t>
+          <t>balance</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>sell</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Butterfly, Shark</t>
+          <t>ABCD Ext</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -4802,7 +4799,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -4812,19 +4809,19 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>sell</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Bat, Cypher, Shark</t>
+          <t>Deep Crab</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -4835,64 +4832,757 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>HCKT</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SGA</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Bat, ABCD Ext</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SGA</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Deep Crab, Butterfly, ABCD Ext</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BAH</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>HGBL</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Deep Crab</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Cypher</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>failed auction low</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>VRRM</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>ABCD Ext</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>PBH</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>ABCD Ext</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>OTEX.TO</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Butterfly, ABCD Ext</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>PET.TO</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ABCD Ext</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>MMS</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>failed auction low</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>NUS</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
           <t>GIB-A.TO</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>sell</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Alternate Bat, Butterfly, Shark</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>VRRM</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Deep Crab, ABCD Ext</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>sell</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Crab, Deep Crab</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Butterfly, ABCD Ext</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Deep Crab</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>JBI</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>BAH</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CINT</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Cypher</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>FISV</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Crab, Bat</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>GPMT</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>balance</t>
         </is>
@@ -4916,7 +5606,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>DEFINITIONS &amp; METHOD</t>
         </is>
